--- a/gte/nodes/P/compressor_parameters.xlsx
+++ b/gte/nodes/P/compressor_parameters.xlsx
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.4</v>
+        <v>0.73</v>
       </c>
       <c r="C3">
         <v>0.2882</v>
@@ -1060,31 +1060,31 @@
         <v>336.02406855230237</v>
       </c>
       <c r="U3">
-        <v>334.4877579556225</v>
+        <v>328.84130437267061</v>
       </c>
       <c r="V3">
-        <v>318.59427847134447</v>
+        <v>315.22317752712297</v>
       </c>
       <c r="W3">
-        <v>361.1995816426994</v>
+        <v>359.5743839777017</v>
       </c>
       <c r="X3">
-        <v>142.68989460703892</v>
+        <v>197.54520591214214</v>
       </c>
       <c r="Y3">
-        <v>412.35898541632594</v>
+        <v>425.13284755474649</v>
       </c>
       <c r="Z3">
-        <v>158.19817162266753</v>
+        <v>175.76039685449413</v>
       </c>
       <c r="AA3">
-        <v>220.5189546794324</v>
+        <v>176.25327233457023</v>
       </c>
       <c r="AB3">
-        <v>276.25149148286823</v>
+        <v>266.9474463775349</v>
       </c>
       <c r="AC3">
-        <v>188.09432338647028</v>
+        <v>163.38579828187841</v>
       </c>
       <c r="AD3">
         <v>168.13150611929245</v>
@@ -1096,103 +1096,103 @@
         <v>205.57130326749973</v>
       </c>
       <c r="AG3">
-        <v>8.736947578101262E-15</v>
+        <v>107.73440551488409</v>
       </c>
       <c r="AH3">
-        <v>343.57000219576787</v>
+        <v>385.54468251886942</v>
       </c>
       <c r="AI3">
-        <v>77.605062658285007</v>
+        <v>112.99329724268371</v>
       </c>
       <c r="AJ3">
-        <v>142.68989460703892</v>
+        <v>165.58202271751952</v>
       </c>
       <c r="AK3">
-        <v>228.03417823822338</v>
+        <v>179.14585077927848</v>
       </c>
       <c r="AL3">
-        <v>137.85541612341035</v>
+        <v>134.62626742458468</v>
       </c>
       <c r="AM3">
-        <v>0.45913244963441074</v>
+        <v>0.63564006795125694</v>
       </c>
       <c r="AN3">
-        <v>1.2271709797244539</v>
+        <v>1.2651857034716378</v>
       </c>
       <c r="AO3">
-        <v>0.47079416752566305</v>
+        <v>0.52305895113920065</v>
       </c>
       <c r="AP3">
-        <v>0.42659227793314347</v>
+        <v>0.60073112253644179</v>
       </c>
       <c r="AQ3">
-        <v>1.2943075669622077</v>
+        <v>1.3486725528555605</v>
       </c>
       <c r="AR3">
-        <v>0.43797994145839858</v>
+        <v>0.48880121801277582</v>
       </c>
       <c r="AS3">
-        <v>0.65927361894269776</v>
+        <v>0.53598276734368266</v>
       </c>
       <c r="AT3">
-        <v>0.86709495477557774</v>
+        <v>0.84685221585448223</v>
       </c>
       <c r="AU3">
-        <v>0.52074900677081681</v>
+        <v>0.45438664588523764</v>
       </c>
       <c r="AV3">
-        <v>278.04571894242946</v>
+        <v>268.73762955153569</v>
       </c>
       <c r="AW3">
-        <v>252.59494606209694</v>
+        <v>247.2777256202283</v>
       </c>
       <c r="AX3">
-        <v>324.67076909257463</v>
+        <v>321.75566549280512</v>
       </c>
       <c r="AY3">
-        <v>89.397764756258482</v>
+        <v>79.377079965523237</v>
       </c>
       <c r="AZ3">
-        <v>59.312763059530468</v>
+        <v>55.05256792507641</v>
       </c>
       <c r="BA3">
-        <v>142.91829845374289</v>
+        <v>138.47294071061842</v>
       </c>
       <c r="BB3">
-        <v>1.1197388624857805</v>
+        <v>1.0286625770690392</v>
       </c>
       <c r="BC3">
-        <v>0.81776741769380012</v>
+        <v>0.775351957748007</v>
       </c>
       <c r="BD3">
-        <v>1.5330310499855095</v>
+        <v>1.498804597221741</v>
       </c>
       <c r="BE3">
-        <v>90</v>
+        <v>56.9503331676176</v>
       </c>
       <c r="BF3">
-        <v>33.573013124947558</v>
+        <v>24.9222443878399</v>
       </c>
       <c r="BG3">
-        <v>60.6228674488778</v>
+        <v>49.992896453076206</v>
       </c>
       <c r="BH3">
-        <v>40.320610109411348</v>
+        <v>69.96023580201512</v>
       </c>
       <c r="BI3">
-        <v>124.36498285022995</v>
+        <v>137.84872687521778</v>
       </c>
       <c r="BJ3">
-        <v>47.130551913836882</v>
+        <v>55.484990380630862</v>
       </c>
       <c r="BK3">
-        <v>84.044372740818616</v>
+        <v>67.888491073202673</v>
       </c>
       <c r="BL3">
-        <v>27.049854323930237</v>
+        <v>25.070652065236303</v>
       </c>
       <c r="BM3">
-        <v>0.034286025101377238</v>
+        <v>-0.38651950343443486</v>
       </c>
     </row>
   </sheetData>
@@ -1864,7 +1864,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.4</v>
+        <v>0.73</v>
       </c>
       <c r="C3">
         <v>0.2882</v>
@@ -1921,31 +1921,31 @@
         <v>336.02406855230237</v>
       </c>
       <c r="U3">
-        <v>334.4877579556225</v>
+        <v>332.45476262963768</v>
       </c>
       <c r="V3">
-        <v>347.17935050319494</v>
+        <v>348.0345565822368</v>
       </c>
       <c r="W3">
-        <v>363.15088872175727</v>
+        <v>362.35287735190809</v>
       </c>
       <c r="X3">
-        <v>142.68989460703892</v>
+        <v>164.67192859919271</v>
       </c>
       <c r="Y3">
-        <v>273.41019571633814</v>
+        <v>267.91097603131885</v>
       </c>
       <c r="Z3">
-        <v>133.97683191452325</v>
+        <v>144.39035217267798</v>
       </c>
       <c r="AA3">
-        <v>353.8459306548404</v>
+        <v>280.5926220540623</v>
       </c>
       <c r="AB3">
-        <v>152.11101090667347</v>
+        <v>141.98913900526927</v>
       </c>
       <c r="AC3">
-        <v>263.75209377832175</v>
+        <v>269.19128753201915</v>
       </c>
       <c r="AD3">
         <v>323.80014919394682</v>
@@ -1957,103 +1957,103 @@
         <v>334.42819155477991</v>
       </c>
       <c r="AG3">
-        <v>8.736947578101262E-15</v>
+        <v>82.19755498559401</v>
       </c>
       <c r="AH3">
-        <v>242.97269309595745</v>
+        <v>242.97269309595748</v>
       </c>
       <c r="AI3">
-        <v>90.044501846578143</v>
+        <v>90.044501846578115</v>
       </c>
       <c r="AJ3">
         <v>142.68989460703892</v>
       </c>
       <c r="AK3">
-        <v>125.36907725330042</v>
+        <v>112.87409573392633</v>
       </c>
       <c r="AL3">
-        <v>99.2057416536664</v>
+        <v>112.87409573392633</v>
       </c>
       <c r="AM3">
-        <v>0.45913244963441074</v>
+        <v>0.52986391343259476</v>
       </c>
       <c r="AN3">
-        <v>0.81366253582451831</v>
+        <v>0.79729698287852957</v>
       </c>
       <c r="AO3">
-        <v>0.39871201039776011</v>
+        <v>0.42970241029089712</v>
       </c>
       <c r="AP3">
-        <v>0.42659227793314347</v>
+        <v>0.49532131017368236</v>
       </c>
       <c r="AQ3">
-        <v>0.78751859901823873</v>
+        <v>0.76978268670287742</v>
       </c>
       <c r="AR3">
-        <v>0.36892882841648506</v>
+        <v>0.39847993819695726</v>
       </c>
       <c r="AS3">
-        <v>1.0578740842939496</v>
+        <v>0.844002413545355</v>
       </c>
       <c r="AT3">
-        <v>0.43813380803382096</v>
+        <v>0.40797425519933611</v>
       </c>
       <c r="AU3">
-        <v>0.7262878929105584</v>
+        <v>0.74289816462692881</v>
       </c>
       <c r="AV3">
-        <v>278.04571894242946</v>
+        <v>274.6761019128972</v>
       </c>
       <c r="AW3">
-        <v>299.95526216687159</v>
+        <v>301.4348404322235</v>
       </c>
       <c r="AX3">
-        <v>328.1881797823649</v>
+        <v>326.74740047377918</v>
       </c>
       <c r="AY3">
-        <v>89.397764756258482</v>
+        <v>85.67180670539507</v>
       </c>
       <c r="AZ3">
-        <v>108.29693022842736</v>
+        <v>110.18002365692928</v>
       </c>
       <c r="BA3">
-        <v>148.41679033894022</v>
+        <v>146.14659000752067</v>
       </c>
       <c r="BB3">
-        <v>1.1197388624857805</v>
+        <v>1.0862339043800009</v>
       </c>
       <c r="BC3">
-        <v>1.2573783118239024</v>
+        <v>1.2729628157325739</v>
       </c>
       <c r="BD3">
-        <v>1.574948670113445</v>
+        <v>1.5576965190223802</v>
       </c>
       <c r="BE3">
-        <v>90</v>
+        <v>60.055592497744023</v>
       </c>
       <c r="BF3">
-        <v>27.2928341136952</v>
+        <v>24.917444116007427</v>
       </c>
       <c r="BG3">
-        <v>47.771414899620616</v>
+        <v>51.419135729614055</v>
       </c>
       <c r="BH3">
-        <v>23.781779037583235</v>
+        <v>30.565993775357981</v>
       </c>
       <c r="BI3">
-        <v>55.506923180366648</v>
+        <v>52.650419990882547</v>
       </c>
       <c r="BJ3">
-        <v>22.094327253489634</v>
+        <v>24.790914632788905</v>
       </c>
       <c r="BK3">
-        <v>31.725144142783414</v>
+        <v>22.084426215524566</v>
       </c>
       <c r="BL3">
-        <v>20.478580785925416</v>
+        <v>26.501691613606628</v>
       </c>
       <c r="BM3">
-        <v>0.62786435246725081</v>
+        <v>0.5019710269234936</v>
       </c>
     </row>
   </sheetData>
@@ -2725,7 +2725,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.4</v>
+        <v>0.73</v>
       </c>
       <c r="C3">
         <v>0.2882</v>
@@ -2782,31 +2782,31 @@
         <v>336.02406855230237</v>
       </c>
       <c r="U3">
-        <v>334.4877579556225</v>
+        <v>333.4364486891979</v>
       </c>
       <c r="V3">
-        <v>353.81635665779311</v>
+        <v>355.09462941568722</v>
       </c>
       <c r="W3">
-        <v>365.0406978092206</v>
+        <v>363.31013132450033</v>
       </c>
       <c r="X3">
-        <v>142.68989460703892</v>
+        <v>154.46507815115385</v>
       </c>
       <c r="Y3">
-        <v>226.8448356334581</v>
+        <v>216.61357384038726</v>
       </c>
       <c r="Z3">
-        <v>105.16469694117819</v>
+        <v>131.79748977088323</v>
       </c>
       <c r="AA3">
-        <v>449.20516015409993</v>
+        <v>379.46970623710644</v>
       </c>
       <c r="AB3">
-        <v>234.14787726455651</v>
+        <v>246.17841972600633</v>
       </c>
       <c r="AC3">
-        <v>338.80609640304971</v>
+        <v>361.96794851563516</v>
       </c>
       <c r="AD3">
         <v>425.93998390160874</v>
@@ -2818,103 +2818,103 @@
         <v>425.93998390160874</v>
       </c>
       <c r="AG3">
-        <v>8.736947578101262E-15</v>
+        <v>71.943319034385524</v>
       </c>
       <c r="AH3">
-        <v>209.0179692467033</v>
+        <v>196.9086048023635</v>
       </c>
       <c r="AI3">
-        <v>91.204060836546546</v>
+        <v>79.5589226239994</v>
       </c>
       <c r="AJ3">
-        <v>142.68989460703892</v>
+        <v>136.68803610615922</v>
       </c>
       <c r="AK3">
-        <v>88.147989118044023</v>
+        <v>90.268719536124649</v>
       </c>
       <c r="AL3">
-        <v>52.358693353189913</v>
+        <v>105.07595415134018</v>
       </c>
       <c r="AM3">
-        <v>0.45913244963441074</v>
+        <v>0.497021389705417</v>
       </c>
       <c r="AN3">
-        <v>0.67508508128830524</v>
+        <v>0.64463707844984686</v>
       </c>
       <c r="AO3">
-        <v>0.31296775077529676</v>
+        <v>0.39222633765107473</v>
       </c>
       <c r="AP3">
-        <v>0.42659227793314347</v>
+        <v>0.4632519292908302</v>
       </c>
       <c r="AQ3">
-        <v>0.64113722094781411</v>
+        <v>0.61001647419119709</v>
       </c>
       <c r="AR3">
-        <v>0.28809033505666781</v>
+        <v>0.36276855063302577</v>
       </c>
       <c r="AS3">
-        <v>1.3429644268586276</v>
+        <v>1.138057065233492</v>
       </c>
       <c r="AT3">
-        <v>0.6617779897920929</v>
+        <v>0.69327553652697049</v>
       </c>
       <c r="AU3">
-        <v>0.92813239300818517</v>
+        <v>0.996305682960252</v>
       </c>
       <c r="AV3">
-        <v>278.04571894242946</v>
+        <v>276.30064660853066</v>
       </c>
       <c r="AW3">
-        <v>311.53333537554431</v>
+        <v>313.78842575777674</v>
       </c>
       <c r="AX3">
-        <v>331.6127991021736</v>
+        <v>328.47606561699519</v>
       </c>
       <c r="AY3">
-        <v>89.397764756258482</v>
+        <v>87.454020220708074</v>
       </c>
       <c r="AZ3">
-        <v>123.66330089121534</v>
+        <v>126.82795466049076</v>
       </c>
       <c r="BA3">
-        <v>153.91386988478254</v>
+        <v>148.87340688986382</v>
       </c>
       <c r="BB3">
-        <v>1.1197388624857805</v>
+        <v>1.1023111015231439</v>
       </c>
       <c r="BC3">
-        <v>1.3824282940324093</v>
+        <v>1.407616575520388</v>
       </c>
       <c r="BD3">
-        <v>1.6164146479156787</v>
+        <v>1.5784095533359244</v>
       </c>
       <c r="BE3">
-        <v>90</v>
+        <v>62.240721705783365</v>
       </c>
       <c r="BF3">
-        <v>22.866342415951745</v>
+        <v>24.628119544419633</v>
       </c>
       <c r="BG3">
-        <v>29.859397269499965</v>
+        <v>52.868585308588187</v>
       </c>
       <c r="BH3">
-        <v>18.520849477471103</v>
+        <v>21.112972530825818</v>
       </c>
       <c r="BI3">
-        <v>22.114757938526825</v>
+        <v>21.511013553437785</v>
       </c>
       <c r="BJ3">
-        <v>8.8900501430783816</v>
+        <v>16.87536474097141</v>
       </c>
       <c r="BK3">
-        <v>3.5939084610557228</v>
+        <v>0.39804102261196517</v>
       </c>
       <c r="BL3">
-        <v>6.9930548535482178</v>
+        <v>28.240465764168551</v>
       </c>
       <c r="BM3">
-        <v>0.75463917788123647</v>
+        <v>0.68440163638305762</v>
       </c>
     </row>
   </sheetData>
